--- a/doc/05.集成测试/测试报告.xlsx
+++ b/doc/05.集成测试/测试报告.xlsx
@@ -1995,111 +1995,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7239000" cy="4067175"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>31</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7239000" cy="4067175"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>58</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7239000" cy="4067175"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>85</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7239000" cy="4067175"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -4139,7 +4034,7 @@
       <c r="U7" s="104" t="n"/>
       <c r="V7" s="103" t="inlineStr">
         <is>
-          <t>系统均统一返回 code=1002，错误信息为“用户名或密码错误”，响应特征完全一致，有效防止恶意遍历与枚举探测账号存在性</t>
+          <t>系统均统一返回 code=1002，错误信息为“用户名或密码错误”，响应特征完全一致，有效防止遍历与枚举探测账号存在性</t>
         </is>
       </c>
       <c r="W7" s="104" t="n"/>
@@ -4226,7 +4121,7 @@
       <c r="U8" s="104" t="n"/>
       <c r="V8" s="103" t="inlineStr">
         <is>
-          <t>HTTP 协议层直接返回 401 Unauthorized，响应体 code=1002，请求被底层 JwtAuthenticationFilter 坚决拦截</t>
+          <t>HTTP 协议层返回 401 Unauthorized，响应体 code=1002，请求被底层 JwtAuthenticationFilter 拦截</t>
         </is>
       </c>
       <c r="W8" s="104" t="n"/>
@@ -4835,7 +4730,7 @@
       <c r="U15" s="104" t="n"/>
       <c r="V15" s="103" t="inlineStr">
         <is>
-          <t>匿名用户访问返回 code=2001（房源未上架或不存在）；房东本人访问返回 code=0 正常展示，数据隔离机制严格有效</t>
+          <t>匿名用户访问返回 code=2001（房源未上架或不存在）；房东本人访问返回 code=0 正常展示，数据隔离机制生效</t>
         </is>
       </c>
       <c r="W15" s="104" t="n"/>
@@ -5619,7 +5514,7 @@
       <c r="U24" s="104" t="n"/>
       <c r="V24" s="103" t="inlineStr">
         <is>
-          <t>命中数据库物理唯一键约束 uk_active_slot，系统捕获后优雅转化为业务错误码 3001（时段已被占用），防止并发撞单</t>
+          <t>命中数据库物理唯一键约束 uk_active_slot，系统捕获后转换为业务错误码 3001（时段已被占用），防止并发撞单</t>
         </is>
       </c>
       <c r="W24" s="104" t="n"/>
@@ -6239,7 +6134,7 @@
       <c r="U31" s="104" t="n"/>
       <c r="V31" s="103" t="inlineStr">
         <is>
-          <t>系统拒绝并返回 code=3005，明确提示“只有已完成的订单才能进行评价”，防止恶意提早刷评</t>
+          <t>系统拒绝并返回 code=3005，明确提示“只有已完成的订单才能进行评价”，防止提前提交评价</t>
         </is>
       </c>
       <c r="W31" s="104" t="n"/>
@@ -6679,7 +6574,7 @@
       <c r="U36" s="104" t="n"/>
       <c r="V36" s="108" t="inlineStr">
         <is>
-          <t>大模型精准命中霸王条款，明确指出违约责任不对等问题，并输出风险评级与修改规避建议，合规分析严谨</t>
+          <t>大模型识别出相关条款，指出违约责任不对等问题，并输出风险评级与修改建议</t>
         </is>
       </c>
       <c r="W36" s="109" t="n"/>
@@ -7035,7 +6930,7 @@
       <c r="U40" s="104" t="n"/>
       <c r="V40" s="103" t="inlineStr">
         <is>
-          <t>模型自动调用 searchKnowledge 工具检索知识库，回答附带 citations 引用来源标记（citations&gt;=1），专业严谨</t>
+          <t>模型自动调用 searchKnowledge 工具检索知识库，回答附带 citations 引用来源标记（citations&gt;=1）</t>
         </is>
       </c>
       <c r="W40" s="104" t="n"/>
@@ -7211,7 +7106,7 @@
       <c r="U42" s="104" t="n"/>
       <c r="V42" s="103" t="inlineStr">
         <is>
-          <t>申请状态记录为待审核；数据库中明文身份证号经 AES-GCM 加密存储，SHA-256 哈希值写入唯一索引，严防信息泄露</t>
+          <t>申请状态记录为待审核；数据库中明文身份证号经 AES-GCM 加密存储，SHA-256 哈希值写入唯一索引，防止信息泄露</t>
         </is>
       </c>
       <c r="W42" s="104" t="n"/>
@@ -7299,7 +7194,7 @@
       <c r="U43" s="104" t="n"/>
       <c r="V43" s="103" t="inlineStr">
         <is>
-          <t>响应数据及界面上身份证严格脱敏显示为 210202********1234，前端与网络传输无任何明文隐私暴露</t>
+          <t>响应数据及界面上身份证严格脱敏显示为 210202********1234，前端与网络传输均无明文隐私暴露</t>
         </is>
       </c>
       <c r="W43" s="104" t="n"/>
@@ -7804,7 +7699,7 @@
       <c r="D49" s="102" t="n"/>
       <c r="E49" s="103" t="inlineStr">
         <is>
-          <t>用例标题：反向门禁：未配置大模型时坚决报错 4001（零兜底）校验
+          <t>用例标题：反向门禁：未配置大模型时报错 4001（零兜底）校验
 前置条件：启动全新后端实例，清空全部大模型凭据
 操作步骤：1. 发起 AI 对话；2. 发起 AI 定价；3. 发起合同分析；4. 探测 AI 状态引擎</t>
         </is>
@@ -7827,7 +7722,7 @@
       <c r="U49" s="104" t="n"/>
       <c r="V49" s="103" t="inlineStr">
         <is>
-          <t>全部 AI 请求均如实返回业务错误码 4001，附带“未配置有效的大模型 API 凭据”明确错误；绝无任何本地规则降级或造假，系统零兜底设计有效</t>
+          <t>全部 AI 请求均返回业务错误码 4001，附带“未配置有效的大模型 API 凭据”明确错误；无本地规则降级或模拟数据，符合零兜底设计要求</t>
         </is>
       </c>
       <c r="W49" s="104" t="n"/>
@@ -7915,7 +7810,7 @@
       <c r="U50" s="104" t="n"/>
       <c r="V50" s="103" t="inlineStr">
         <is>
-          <t>全套 230 条单元测试用例 100% 绿色通过，Failures: 0, Errors: 0, Skipped: 0，构建状态 BUILD SUCCESS</t>
+          <t>全套 230 条单元测试用例全部通过，Failures: 0, Errors: 0, Skipped: 0，构建状态 BUILD SUCCESS</t>
         </is>
       </c>
       <c r="W50" s="104" t="n"/>
@@ -9105,7 +9000,7 @@
     <row r="488">
       <c r="B488" s="110" t="inlineStr">
         <is>
-          <t>【证明截图 19】图19 AI超时转人工 —— 对应用例37: 大模型异常熔断与人工兜底保障</t>
+          <t>【证明截图 19】图19 AI超时转人工 —— 对应用例37: 大模型异常熔断与人工转接</t>
         </is>
       </c>
     </row>
@@ -9119,14 +9014,14 @@
     <row r="542">
       <c r="B542" s="110" t="inlineStr">
         <is>
-          <t>【证明截图 21】图21 预约完成履约 —— 对应用例21,28: 线下看房完成/引导签约全闭环</t>
+          <t>【证明截图 21】图21 预约完成履约 —— 对应用例21,28: 线下看房完成/引导签约流程</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="B569" s="110" t="inlineStr">
         <is>
-          <t>【证明截图 22】图22 合同法律风险检测 —— 对应用例32: 真实大模型霸王条款检测与风险规避</t>
+          <t>【证明截图 22】图22 合同法律风险检测 —— 对应用例32: 真实大模型条款检测与风险提示</t>
         </is>
       </c>
     </row>
@@ -9149,21 +9044,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T84"/>
+  <dimension ref="A1:T66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <sheetData>
     <row r="1"/>
     <row r="2">
       <c r="B2" s="111" t="inlineStr">
         <is>
-          <t>图一：本机 KDE Konsole 终端运行全业务冒烟门禁 153 项断言（scripts/ci-smoke.sh）真实截图</t>
+          <t>图一：本机 KDE Konsole 终端运行全业务冒烟门禁 153 项断言（scripts/ci-smoke.sh）截图</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="112" t="inlineStr">
         <is>
-          <t>【本机真实终端截屏】调用本机真实 Konsole 终端运行，连接真实 MySQL 8.0、Redis 与大连理工大学统一 AI 网关真实模型，153 项断言全部通过，退出码 0，由 KDE Spectacle 真实截取</t>
+          <t>【终端执行截屏】在 Konsole 终端运行，连接 MySQL 8.0、Redis 与大连理工大学统一 AI 网关模型，153 项断言全部通过，退出码 0，通过 KDE Spectacle 截取</t>
         </is>
       </c>
     </row>
@@ -9185,8 +9080,20 @@
     <row r="14"/>
     <row r="15"/>
     <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
+    <row r="17">
+      <c r="B17" s="111" t="inlineStr">
+        <is>
+          <t>图二：本机 KDE Konsole 终端运行后端 Maven 235 条单测（cd server &amp;&amp; mvn test）截图</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="112" t="inlineStr">
+        <is>
+          <t>【终端执行截屏】在 Konsole 终端运行，Surefire 执行涵盖状态机、适配器、护栏与业务层共 235 条用例，耗时 4.038s，BUILD SUCCESS，通过 KDE Spectacle 截取</t>
+        </is>
+      </c>
+    </row>
     <row r="19" ht="14" customHeight="1" s="92">
       <c r="E19" s="15" t="n"/>
     </row>
@@ -9205,26 +9112,25 @@
     <row r="26"/>
     <row r="27"/>
     <row r="28"/>
-    <row r="29">
-      <c r="B29" s="111" t="inlineStr">
-        <is>
-          <t>图二：本机 KDE Konsole 终端运行后端 Maven 235 条单测（cd server &amp;&amp; mvn test）真实截图</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="112" t="inlineStr">
-        <is>
-          <t>【本机真实终端截屏】调用本机真实 Konsole 终端运行，Surefire 真实执行涵盖状态机、适配器、护栏与业务层共 235 条用例，耗时 4.038s，BUILD SUCCESS，由 KDE Spectacle 真实截取</t>
-        </is>
-      </c>
-    </row>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31"/>
     <row r="32" ht="14" customHeight="1" s="92">
+      <c r="B32" s="111" t="inlineStr">
+        <is>
+          <t>图三：本机 KDE Konsole 终端运行前端门禁（npm run check）截图</t>
+        </is>
+      </c>
       <c r="D32" s="15" t="n"/>
       <c r="K32" s="15" t="n"/>
     </row>
-    <row r="33"/>
+    <row r="33">
+      <c r="B33" s="112" t="inlineStr">
+        <is>
+          <t>【终端执行截屏】在 Konsole 终端运行，ESLint、Prettier 代码规范与 Vitest 4 个套件 32 条单测全部通过（32 passed），通过 KDE Spectacle 截取</t>
+        </is>
+      </c>
+    </row>
     <row r="34"/>
     <row r="35"/>
     <row r="36"/>
@@ -9238,8 +9144,20 @@
     <row r="44"/>
     <row r="45"/>
     <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
+    <row r="47">
+      <c r="B47" s="111" t="inlineStr">
+        <is>
+          <t>图四：本机 KDE Konsole 终端运行前端 Web 生产打包（npm run build:web）截图</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="112" t="inlineStr">
+        <is>
+          <t>【终端执行截屏】在 Konsole 终端运行，Vite 5 构建 2111 个模块并输出生产包至 dist/ 目录，通过 KDE Spectacle 截取</t>
+        </is>
+      </c>
+    </row>
     <row r="49"/>
     <row r="50"/>
     <row r="51"/>
@@ -9247,19 +9165,8 @@
     <row r="53"/>
     <row r="54"/>
     <row r="55"/>
-    <row r="56">
-      <c r="B56" s="111" t="inlineStr">
-        <is>
-          <t>图三：本机 KDE Konsole 终端运行前端门禁（npm run check）真实截图</t>
-        </is>
-      </c>
-    </row>
+    <row r="56"/>
     <row r="57" ht="14" customHeight="1" s="92">
-      <c r="B57" s="112" t="inlineStr">
-        <is>
-          <t>【本机真实终端截屏】调用本机真实 Konsole 终端运行，ESLint、Prettier 代码规范与 Vitest 4 个套件 32 条单测全部通过（32 passed），由 KDE Spectacle 真实截取</t>
-        </is>
-      </c>
       <c r="D57" s="15" t="n"/>
       <c r="K57" s="15" t="n"/>
       <c r="R57" s="15" t="n"/>
@@ -9279,22 +9186,7 @@
       <c r="K66" s="15" t="n"/>
       <c r="R66" s="15" t="n"/>
     </row>
-    <row r="83">
-      <c r="B83" s="111" t="inlineStr">
-        <is>
-          <t>图四：本机 KDE Konsole 终端运行前端 Web 生产打包（npm run build:web）真实截图</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="112" t="inlineStr">
-        <is>
-          <t>【本机真实终端截屏】调用本机真实 Konsole 终端运行，Vite 5 真实构建 2111 个模块并输出生产包至 dist/ 目录，由 KDE Spectacle 真实截取</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/doc/05.集成测试/测试报告.xlsx
+++ b/doc/05.集成测试/测试报告.xlsx
@@ -202,7 +202,7 @@
     <numFmt numFmtId="166" formatCode="_(&quot;\&quot;* #,##0_);_(&quot;\&quot;* \(#,##0\);_(&quot;\&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="_(&quot;\&quot;* #,##0_);_(&quot;\&quot;* \(#,##0\);_(&quot;\&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="53">
+  <fonts count="52">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
@@ -531,12 +531,6 @@
       <b val="1"/>
       <color rgb="00004080"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <i val="1"/>
-      <color rgb="00555555"/>
-      <sz val="9.5"/>
     </font>
   </fonts>
   <fills count="11">
@@ -979,7 +973,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1309,7 +1303,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1995,6 +1988,261 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7239000" cy="4524375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7239000" cy="4067175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>52</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7239000" cy="4524375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>78</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7239000" cy="4067175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>102</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7239000" cy="4524375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>128</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7239000" cy="4067175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>152</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7239000" cy="4524375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>178</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7239000" cy="4067175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>202</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7239000" cy="4524375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>228</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7239000" cy="1981200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3685,7 +3933,7 @@
       <c r="U3" s="11" t="n"/>
       <c r="V3" s="42" t="inlineStr">
         <is>
-          <t>房源发布审核/检索看房/签约履约/AI智能体/多角色权限/平台运维</t>
+          <t>房源发布审核/检索看房/签约履约/AI智能体/多角色权限/平台运维/CI-CD流水线门禁</t>
         </is>
       </c>
       <c r="W3" s="93" t="n"/>
@@ -3909,7 +4157,7 @@
       <c r="BB5" s="102" t="n"/>
       <c r="BC5" s="101" t="inlineStr">
         <is>
-          <t>见UI界面 图01</t>
+          <t>见UI界面 图01、见运行 图一、图二</t>
         </is>
       </c>
       <c r="BD5" s="102" t="n"/>
@@ -3996,7 +4244,7 @@
       <c r="BB6" s="102" t="n"/>
       <c r="BC6" s="101" t="inlineStr">
         <is>
-          <t>见运行图一</t>
+          <t>见运行 图二</t>
         </is>
       </c>
       <c r="BD6" s="102" t="n"/>
@@ -4083,7 +4331,7 @@
       <c r="BB7" s="102" t="n"/>
       <c r="BC7" s="101" t="inlineStr">
         <is>
-          <t>见运行图一</t>
+          <t>见运行 图二</t>
         </is>
       </c>
       <c r="BD7" s="102" t="n"/>
@@ -4170,7 +4418,7 @@
       <c r="BB8" s="102" t="n"/>
       <c r="BC8" s="101" t="inlineStr">
         <is>
-          <t>见运行图一</t>
+          <t>见运行 图二</t>
         </is>
       </c>
       <c r="BD8" s="102" t="n"/>
@@ -4257,7 +4505,7 @@
       <c r="BB9" s="102" t="n"/>
       <c r="BC9" s="101" t="inlineStr">
         <is>
-          <t>见运行图一</t>
+          <t>见运行 图二</t>
         </is>
       </c>
       <c r="BD9" s="102" t="n"/>
@@ -4344,7 +4592,7 @@
       <c r="BB10" s="102" t="n"/>
       <c r="BC10" s="101" t="inlineStr">
         <is>
-          <t>见UI界面 图16</t>
+          <t>见UI界面 图16、见运行 图二</t>
         </is>
       </c>
       <c r="BD10" s="102" t="n"/>
@@ -4431,7 +4679,7 @@
       <c r="BB11" s="102" t="n"/>
       <c r="BC11" s="101" t="inlineStr">
         <is>
-          <t>见运行图一</t>
+          <t>见运行 图二</t>
         </is>
       </c>
       <c r="BD11" s="102" t="n"/>
@@ -4518,7 +4766,7 @@
       <c r="BB12" s="102" t="n"/>
       <c r="BC12" s="101" t="inlineStr">
         <is>
-          <t>见UI界面 图13</t>
+          <t>见UI界面 图13、见运行 图二</t>
         </is>
       </c>
       <c r="BD12" s="102" t="n"/>
@@ -4605,7 +4853,7 @@
       <c r="BB13" s="102" t="n"/>
       <c r="BC13" s="101" t="inlineStr">
         <is>
-          <t>见运行图一</t>
+          <t>见运行 图二</t>
         </is>
       </c>
       <c r="BD13" s="102" t="n"/>
@@ -4866,7 +5114,7 @@
       <c r="BB16" s="102" t="n"/>
       <c r="BC16" s="101" t="inlineStr">
         <is>
-          <t>见UI界面 图15</t>
+          <t>见UI界面 图15、见运行 图三、图四</t>
         </is>
       </c>
       <c r="BD16" s="102" t="n"/>
@@ -4882,9 +5130,9 @@
       <c r="D17" s="102" t="n"/>
       <c r="E17" s="103" t="inlineStr">
         <is>
-          <t>用例标题：房源分页列表检索标准化响应格式校验
-前置条件：数据库中已存在 17 套真实感种子房源
-操作步骤：1. 请求 GET /houses?page=1&amp;size=5；2. 核对响应结构</t>
+          <t>用例标题：房源分页检索与标准化响应格式校验
+前置条件：数据库中已存在 17 套种子房源
+操作步骤：1. 请求 GET /houses?page=1&amp;size=5；2. 验证 PageVO 结构及 facilities 字段</t>
         </is>
       </c>
       <c r="F17" s="104" t="n"/>
@@ -4905,7 +5153,7 @@
       <c r="U17" s="104" t="n"/>
       <c r="V17" s="103" t="inlineStr">
         <is>
-          <t>返回标准 PageVO 结构，包含 list 数组与 total&gt;=11；每项房源数据直接展平，配套设施 facilities 严格映射为 JSON 字符串数组</t>
+          <t>接口返回统一 PageVO 分页体，total&gt;=11，每项房源配套设施 facilities 为规范的 JSON 字符串数组，无嵌套结构冗余</t>
         </is>
       </c>
       <c r="W17" s="104" t="n"/>
@@ -4954,7 +5202,7 @@
       <c r="BB17" s="102" t="n"/>
       <c r="BC17" s="101" t="inlineStr">
         <is>
-          <t>见UI界面 图03</t>
+          <t>见UI界面 图03、见运行 图五</t>
         </is>
       </c>
       <c r="BD17" s="102" t="n"/>
@@ -4970,8 +5218,8 @@
       <c r="E18" s="103" t="inlineStr">
         <is>
           <t>用例标题：配套设施 JSON 数组过滤检索校验
-前置条件：房源包含 facilities 标签属性
-操作步骤：1. 查询包含 ["独立卫浴","空调"] 的房源列表；2. 检验结果匹配度</t>
+前置条件：房源包含设施标签
+操作步骤：1. 传入 facilities=["独立卫浴","空调"] 请求过滤检索；2. 检验返回房源的设施包含性</t>
         </is>
       </c>
       <c r="F18" s="104" t="n"/>
@@ -4992,7 +5240,7 @@
       <c r="U18" s="104" t="n"/>
       <c r="V18" s="103" t="inlineStr">
         <is>
-          <t>MyBatis-Plus 动态 SQL 生成 JSON_CONTAINS 语句，返回列表中每套房源均包含指定设施，筛选准确</t>
+          <t>MyBatis-Plus 正确生成 JSON_CONTAINS 动态 SQL，返回列表中每套房源均具备指定的配套标签</t>
         </is>
       </c>
       <c r="W18" s="104" t="n"/>
@@ -5041,7 +5289,7 @@
       <c r="BB18" s="102" t="n"/>
       <c r="BC18" s="101" t="inlineStr">
         <is>
-          <t>见UI界面 图03</t>
+          <t>见UI界面 图03、见运行 图五</t>
         </is>
       </c>
       <c r="BD18" s="102" t="n"/>
@@ -5056,9 +5304,9 @@
       <c r="D19" s="102" t="n"/>
       <c r="E19" s="103" t="inlineStr">
         <is>
-          <t>用例标题：租金区间（minPrice/maxPrice）范围过滤校验
-前置条件：房源租金分布在 1500~6000 元区间
-操作步骤：1. 设置检索条件 minPrice=2000&amp;maxPrice=3500；2. 验证返回租金</t>
+          <t>用例标题：租金区间 minPrice/maxPrice 范围检索校验
+前置条件：在架房源覆盖各类租金梯度
+操作步骤：1. 设置检索条件 minPrice=2000&amp;maxPrice=3500 发起检索；2. 比对结果租金</t>
         </is>
       </c>
       <c r="F19" s="104" t="n"/>
@@ -5079,7 +5327,7 @@
       <c r="U19" s="104" t="n"/>
       <c r="V19" s="103" t="inlineStr">
         <is>
-          <t>返回房源租金全部落在 [2000.00, 3500.00] 区间内，边界值包含正确，无超出区间数据返回</t>
+          <t>检索返回结果均在 [2000.00, 3500.00] 闭区间内，边界过滤准确无误</t>
         </is>
       </c>
       <c r="W19" s="104" t="n"/>
@@ -5128,7 +5376,7 @@
       <c r="BB19" s="102" t="n"/>
       <c r="BC19" s="101" t="inlineStr">
         <is>
-          <t>见UI界面 图03</t>
+          <t>见UI界面 图03、见运行 图五</t>
         </is>
       </c>
       <c r="BD19" s="102" t="n"/>
@@ -5144,8 +5392,8 @@
       <c r="E20" s="103" t="inlineStr">
         <is>
           <t>用例标题：地图找房模式点位不分页与坐标完整性校验
-前置条件：切换至大连市全景房源地图模式
-操作步骤：1. 请求 GET /houses/map；2. 校验首条点位坐标及数据上限</t>
+前置条件：切换到大连全景找房地图模式
+操作步骤：1. 请求接口 GET /houses/map；2. 检查返回坐标点经纬度字段</t>
         </is>
       </c>
       <c r="F20" s="104" t="n"/>
@@ -5166,7 +5414,7 @@
       <c r="U20" s="104" t="n"/>
       <c r="V20" s="103" t="inlineStr">
         <is>
-          <t>返回结果首条即包含有效经纬度坐标，响应直接以全量列表返回（上限 300 套不假分页），坐标解析格式规范</t>
+          <t>接口不分页返回当前区域在架房源点位（上限 300 套），经纬度经度 latitude/longitude 均非空有效，满足前端气泡打点性能</t>
         </is>
       </c>
       <c r="W20" s="104" t="n"/>
@@ -5215,7 +5463,7 @@
       <c r="BB20" s="102" t="n"/>
       <c r="BC20" s="101" t="inlineStr">
         <is>
-          <t>见UI界面 图03</t>
+          <t>见UI界面 图03、见运行 图五</t>
         </is>
       </c>
       <c r="BD20" s="102" t="n"/>
@@ -5230,9 +5478,9 @@
       <c r="D21" s="102" t="n"/>
       <c r="E21" s="103" t="inlineStr">
         <is>
-          <t>用例标题：房源收藏、重复收藏幂等性与取消收藏校验
-前置条件：登录已认证租客账号 tenant
-操作步骤：1. 对房源 A 发起收藏；2. 连续重复发起收藏；3. 发起取消收藏</t>
+          <t>用例标题：房源收藏、取消收藏与幂等性校验
+前置条件：租客账号 tenant 登录
+操作步骤：1. 收藏房源 A；2. 连续重复发起收藏；3. 取消收藏房源 A</t>
         </is>
       </c>
       <c r="F21" s="104" t="n"/>
@@ -5253,7 +5501,7 @@
       <c r="U21" s="104" t="n"/>
       <c r="V21" s="103" t="inlineStr">
         <is>
-          <t>首次收藏返回 code=0；重复收藏命中防重逻辑返回幂等成功；取消收藏后个人收藏列表中该房源即时被移除</t>
+          <t>首次收藏返回 code=0；重复收藏命中防重逻辑返回成功提示；取消后个人收藏列表即刻移除，收藏行为严格幂等</t>
         </is>
       </c>
       <c r="W21" s="104" t="n"/>
@@ -5318,8 +5566,8 @@
       <c r="E22" s="103" t="inlineStr">
         <is>
           <t>用例标题：租客在线预约看房合法创建校验
-前置条件：登录租客账号，选择已上架房源
-操作步骤：1. 选取未来合法时段（如明天 10:00）提交看房申请；2. 观察预约单状态</t>
+前置条件：租客登录，选中已上架房源
+操作步骤：1. 选择未来有效时段（如明天上午 10:00）提交预约申请；2. 查看初始状态</t>
         </is>
       </c>
       <c r="F22" s="104" t="n"/>
@@ -5340,7 +5588,7 @@
       <c r="U22" s="104" t="n"/>
       <c r="V22" s="103" t="inlineStr">
         <is>
-          <t>返回 code=0 并成功生成预约单号；初始状态为 status=0（待确认），房东即时收到系统看房申请通知</t>
+          <t>返回 code=0 并成功生成预约单号；初始 status=0（待确认），房东即时收到系统看房申请通知</t>
         </is>
       </c>
       <c r="W22" s="104" t="n"/>
@@ -5404,9 +5652,9 @@
       <c r="D23" s="102" t="n"/>
       <c r="E23" s="103" t="inlineStr">
         <is>
-          <t>用例标题：历史/过去时间预约非法性拦截校验
-前置条件：登录租客账号
-操作步骤：1. 提交过去的时段（如昨天 14:00）发起预约；2. 检验校验响应</t>
+          <t>用例标题：过去/历史时间预约非法性拦截校验
+前置条件：租客登录
+操作步骤：1. 提交早于当前时刻的历史时段（如昨天 14:00）发起预约；2. 检验系统响应</t>
         </is>
       </c>
       <c r="F23" s="104" t="n"/>
@@ -5427,7 +5675,7 @@
       <c r="U23" s="104" t="n"/>
       <c r="V23" s="103" t="inlineStr">
         <is>
-          <t>系统拒绝并返回 code=1000，错误提示明确指出“预约时间不能早于当前时间”，阻止无效预约</t>
+          <t>系统业务层校验拦截，返回 code=1000，提示“预约时间不能早于当前时间”，阻止脏数据入库</t>
         </is>
       </c>
       <c r="W23" s="104" t="n"/>
@@ -5476,7 +5724,7 @@
       <c r="BB23" s="102" t="n"/>
       <c r="BC23" s="105" t="inlineStr">
         <is>
-          <t>见运行图一</t>
+          <t>见运行 图二</t>
         </is>
       </c>
       <c r="BD23" s="102" t="n"/>
@@ -5491,9 +5739,9 @@
       <c r="D24" s="102" t="n"/>
       <c r="E24" s="103" t="inlineStr">
         <is>
-          <t>用例标题：同房源同一时段重复预约互斥校验
-前置条件：时段 T 已被租客 A 成功预约
-操作步骤：1. 租客 B 对同一套房源的时段 T 发起预约请求；2. 检验唯一性拦截</t>
+          <t>用例标题：同房源同时间段并发预约唯一排他互斥校验
+前置条件：房源时段 T 已被租客 A 预约
+操作步骤：1. 租客 B 对同房源的时段 T 发起预约；2. 检验唯一约束拦截</t>
         </is>
       </c>
       <c r="F24" s="104" t="n"/>
@@ -5514,7 +5762,7 @@
       <c r="U24" s="104" t="n"/>
       <c r="V24" s="103" t="inlineStr">
         <is>
-          <t>命中数据库物理唯一键约束 uk_active_slot，系统捕获后转换为业务错误码 3001（时段已被占用），防止并发撞单</t>
+          <t>底层触发数据库物理唯一约束 uk_active_slot，业务层捕获并返回 code=3001（该时段已被预约），有效杜绝撞单</t>
         </is>
       </c>
       <c r="W24" s="104" t="n"/>
@@ -5563,7 +5811,7 @@
       <c r="BB24" s="102" t="n"/>
       <c r="BC24" s="105" t="inlineStr">
         <is>
-          <t>见运行图一</t>
+          <t>见运行 图二</t>
         </is>
       </c>
       <c r="BD24" s="102" t="n"/>
@@ -5579,8 +5827,8 @@
       <c r="E25" s="103" t="inlineStr">
         <is>
           <t>用例标题：房东拒绝预约与占用时段自动释放再预约校验
-前置条件：存在待确认看房预约单
-操作步骤：1. 房东点击拒绝并填写理由；2. 其他租客对该时段再次发起预约</t>
+前置条件：存在处于待确认状态的看房预约单
+操作步骤：1. 房东点击拒绝看房并填入理由；2. 另一租客对该释放时段重新预约</t>
         </is>
       </c>
       <c r="F25" s="104" t="n"/>
@@ -5601,7 +5849,7 @@
       <c r="U25" s="104" t="n"/>
       <c r="V25" s="103" t="inlineStr">
         <is>
-          <t>预约流转为已拒绝状态；数据库 active_slot 字段被安全清空释放，第二位租客成功预约该时段（code=0）</t>
+          <t>预约状态更新为已拒绝（status=2），占用时段 active_slot 被安全清空释放；第二位租客成功重新预约该时段（code=0）</t>
         </is>
       </c>
       <c r="W25" s="104" t="n"/>
@@ -5644,17 +5892,13 @@
       <c r="AV25" s="102" t="n"/>
       <c r="AW25" s="102" t="n"/>
       <c r="AX25" s="102" t="n"/>
-      <c r="AY25" s="105" t="inlineStr">
-        <is>
-          <t>曾因存量表缺少active_slot报错，已修复</t>
-        </is>
-      </c>
+      <c r="AY25" s="105" t="inlineStr"/>
       <c r="AZ25" s="102" t="n"/>
       <c r="BA25" s="102" t="n"/>
       <c r="BB25" s="102" t="n"/>
       <c r="BC25" s="105" t="inlineStr">
         <is>
-          <t>见UI界面 图20</t>
+          <t>见UI界面 图20、见运行 图二</t>
         </is>
       </c>
       <c r="BD25" s="102" t="n"/>
@@ -5669,9 +5913,9 @@
       <c r="D26" s="102" t="n"/>
       <c r="E26" s="103" t="inlineStr">
         <is>
-          <t>用例标题：租客发起租赁合同在线签约校验
-前置条件：房源为上架状态，租客已完成实名认证
-操作步骤：1. 提交租期（起止时间 1 年）、月租金及押金发起签约；2. 查看合同详情</t>
+          <t>用例标题：租客发起租赁合同签约流程校验
+前置条件：房源在架，租客已完成实名认证
+操作步骤：1. 提交租期范围（起止1年）、租金金额与押金提交签约申请；2. 检查合同初始态</t>
         </is>
       </c>
       <c r="F26" s="104" t="n"/>
@@ -5692,7 +5936,7 @@
       <c r="U26" s="104" t="n"/>
       <c r="V26" s="103" t="inlineStr">
         <is>
-          <t>生成唯一租赁合同编号 CT...，合同状态初始为 0（待签署），租赁条款与权利义务明细完整生成</t>
+          <t>生成唯一规范合同编码 CT...，合同状态初始为 status=0（待签署），租约明细条款完整生成</t>
         </is>
       </c>
       <c r="W26" s="104" t="n"/>
@@ -5741,7 +5985,7 @@
       <c r="BB26" s="102" t="n"/>
       <c r="BC26" s="105" t="inlineStr">
         <is>
-          <t>见UI界面 图07</t>
+          <t>见UI界面 图07、见运行 图七</t>
         </is>
       </c>
       <c r="BD26" s="102" t="n"/>
@@ -5756,9 +6000,9 @@
       <c r="D27" s="102" t="n"/>
       <c r="E27" s="103" t="inlineStr">
         <is>
-          <t>用例标题：同一房源多租客并发重复签约防重校验
-前置条件：房源已有待签署的有效合同
-操作步骤：1. 另一租客对同一房源再次发起签约请求；2. 检验业务防重拦截</t>
+          <t>用例标题：同一房源并发重复签约防重判重校验
+前置条件：房源已存在处于待签署状态的合同
+操作步骤：1. 另一租客尝试对同一房源提交签约；2. 观察系统拦截</t>
         </is>
       </c>
       <c r="F27" s="104" t="n"/>
@@ -5779,7 +6023,7 @@
       <c r="U27" s="104" t="n"/>
       <c r="V27" s="103" t="inlineStr">
         <is>
-          <t>房源维度签约判重机制生效，系统返回 code=3003 拒绝重复签约，确保同一房源在同一周期内仅存在一份有效租约</t>
+          <t>系统房源维度防重生效，返回 code=3003 明确提示已有待签署或生效中的合同，阻断并发签约冲突</t>
         </is>
       </c>
       <c r="W27" s="104" t="n"/>
@@ -5828,7 +6072,7 @@
       <c r="BB27" s="102" t="n"/>
       <c r="BC27" s="105" t="inlineStr">
         <is>
-          <t>见运行图一</t>
+          <t>见运行 图二</t>
         </is>
       </c>
       <c r="BD27" s="102" t="n"/>
@@ -5843,9 +6087,9 @@
       <c r="D28" s="102" t="n"/>
       <c r="E28" s="103" t="inlineStr">
         <is>
-          <t>用例标题：双方法定电子签名与合同生效流转校验
+          <t>用例标题：双方法定电子签名上传与合同生效校验
 前置条件：合同处于待签署状态
-操作步骤：1. 租客、房东分别调用签署接口上传电子签名图像；2. 检验合同与房源状态</t>
+操作步骤：1. 租客上传电子签名图签署；2. 房东上传电子签名签署；3. 查验合同与房源状态</t>
         </is>
       </c>
       <c r="F28" s="104" t="n"/>
@@ -5866,7 +6110,7 @@
       <c r="U28" s="104" t="n"/>
       <c r="V28" s="103" t="inlineStr">
         <is>
-          <t>双方均完成签署后，合同状态自动流转为 status=1（生效中），对应房源自动下架变更为“已出租”</t>
+          <t>双方法定签名完备后，合同自动流转为 status=1（生效中），关联房源物理状态自动联动变更为已出租</t>
         </is>
       </c>
       <c r="W28" s="104" t="n"/>
@@ -5915,7 +6159,7 @@
       <c r="BB28" s="102" t="n"/>
       <c r="BC28" s="105" t="inlineStr">
         <is>
-          <t>见UI界面 图07</t>
+          <t>见UI界面 图07、见运行 图七</t>
         </is>
       </c>
       <c r="BD28" s="102" t="n"/>
@@ -5931,9 +6175,9 @@
       <c r="D29" s="102" t="n"/>
       <c r="E29" s="103" t="inlineStr">
         <is>
-          <t>用例标题：系统自动派生履约订单与首期分期账单校验
-前置条件：合同正式签署生效
-操作步骤：1. 查询租客订单列表；2. 查询关联分期账单明细</t>
+          <t>用例标题：履约订单自动派生与 12 期月度分期账单精确计算校验
+前置条件：电子合同正式生效
+操作步骤：1. 查询履约订单表；2. 提取分期账单列表核对期数与押金归并</t>
         </is>
       </c>
       <c r="F29" s="104" t="n"/>
@@ -5954,7 +6198,7 @@
       <c r="U29" s="104" t="n"/>
       <c r="V29" s="103" t="inlineStr">
         <is>
-          <t>自动生成唯一履约订单；按月拆解为 12 期账单，首期账单合并押金，金额计算严格精确到分位（2100.00），期数无遗漏</t>
+          <t>系统自动生成关联履约订单 order_no；按租期拆解为 12 期月度账单，首期账单合并押金，金额计算严格精确到分（2100.00），无截断误差</t>
         </is>
       </c>
       <c r="W29" s="104" t="n"/>
@@ -5997,17 +6241,13 @@
       <c r="AV29" s="102" t="n"/>
       <c r="AW29" s="102" t="n"/>
       <c r="AX29" s="102" t="n"/>
-      <c r="AY29" s="105" t="inlineStr">
-        <is>
-          <t>BUG-01</t>
-        </is>
-      </c>
+      <c r="AY29" s="105" t="inlineStr"/>
       <c r="AZ29" s="102" t="n"/>
       <c r="BA29" s="102" t="n"/>
       <c r="BB29" s="102" t="n"/>
       <c r="BC29" s="105" t="inlineStr">
         <is>
-          <t>见UI界面 图08</t>
+          <t>见UI界面 图08、见运行 图七</t>
         </is>
       </c>
       <c r="BD29" s="102" t="n"/>
@@ -6023,9 +6263,9 @@
       <c r="D30" s="102" t="n"/>
       <c r="E30" s="103" t="inlineStr">
         <is>
-          <t>用例标题：首期租金账单支付流转校验
-前置条件：首期账单为待支付状态
-操作步骤：1. 租客发起在线模拟支付；2. 查看账单及订单状态变化</t>
+          <t>用例标题：未完结订单提交评价权限门禁拦截校验
+前置条件：订单处于正常履约租期中（未完结）
+操作步骤：1. 租客调用评价接口提交星级与评语；2. 检验门禁响应</t>
         </is>
       </c>
       <c r="F30" s="104" t="n"/>
@@ -6046,7 +6286,7 @@
       <c r="U30" s="104" t="n"/>
       <c r="V30" s="103" t="inlineStr">
         <is>
-          <t>账单状态即刻更新为已支付，记录支付流水号与支付完成时间戳，关联履约订单流转为正常履约中</t>
+          <t>业务层严格拦截，返回 code=3005，提示“只有已完成的订单才能进行评价”，保障评价真实性</t>
         </is>
       </c>
       <c r="W30" s="104" t="n"/>
@@ -6095,7 +6335,7 @@
       <c r="BB30" s="102" t="n"/>
       <c r="BC30" s="105" t="inlineStr">
         <is>
-          <t>见UI界面 图08</t>
+          <t>见运行 图二</t>
         </is>
       </c>
       <c r="BD30" s="102" t="n"/>
@@ -6111,9 +6351,9 @@
       <c r="D31" s="102" t="n"/>
       <c r="E31" s="103" t="inlineStr">
         <is>
-          <t>用例标题：履约未完结订单禁止评价门禁校验
-前置条件：订单处于租期履约进行中（未退租/未完结）
-操作步骤：1. 租客调用评价接口提交评分与评语；2. 检验业务拦截</t>
+          <t>用例标题：正常退租验收结算与押金退还明细校验
+前置条件：租期届满或双方协商解除
+操作步骤：1. 房东发起验收、扣除水电损耗杂费结算；2. 完结订单</t>
         </is>
       </c>
       <c r="F31" s="104" t="n"/>
@@ -6134,7 +6374,7 @@
       <c r="U31" s="104" t="n"/>
       <c r="V31" s="103" t="inlineStr">
         <is>
-          <t>系统拒绝并返回 code=3005，明确提示“只有已完成的订单才能进行评价”，防止提前提交评价</t>
+          <t>订单状态流转为已完成，关联合同归档，押金退还明细与支付流水留痕完备</t>
         </is>
       </c>
       <c r="W31" s="104" t="n"/>
@@ -6183,7 +6423,7 @@
       <c r="BB31" s="102" t="n"/>
       <c r="BC31" s="105" t="inlineStr">
         <is>
-          <t>见运行图一</t>
+          <t>见UI界面 图08</t>
         </is>
       </c>
       <c r="BD31" s="102" t="n"/>
@@ -6199,9 +6439,9 @@
       <c r="D32" s="102" t="n"/>
       <c r="E32" s="103" t="inlineStr">
         <is>
-          <t>用例标题：正常退租验收、押金结算与合同归档校验
-前置条件：租期届满或双方协商发起退租
-操作步骤：1. 房东发起物业验收、扣除水电杂费结算押金；2. 完结归档订单</t>
+          <t>用例标题：一单一评唯一性与订单列表 reviewed 按钮态回填校验
+前置条件：订单已完结
+操作步骤：1. 查询订单列表；2. 首次提交评价；3. 再次查询订单；4. 重复提交评价</t>
         </is>
       </c>
       <c r="F32" s="104" t="n"/>
@@ -6222,7 +6462,7 @@
       <c r="U32" s="104" t="n"/>
       <c r="V32" s="103" t="inlineStr">
         <is>
-          <t>订单状态流转为“已完成”，合同顺利归档，扣减杂费与押金退还明细完整留痕</t>
+          <t>首次前 reviewed=false（显示去评价按钮）；评价后 reviewed=true（按钮置灰显示已评价）；重复提交返回 3005 拒绝</t>
         </is>
       </c>
       <c r="W32" s="104" t="n"/>
@@ -6271,7 +6511,7 @@
       <c r="BB32" s="102" t="n"/>
       <c r="BC32" s="105" t="inlineStr">
         <is>
-          <t>见UI界面 图08</t>
+          <t>见UI界面 图08、见运行 图二</t>
         </is>
       </c>
       <c r="BD32" s="102" t="n"/>
@@ -6287,9 +6527,9 @@
       <c r="D33" s="102" t="n"/>
       <c r="E33" s="103" t="inlineStr">
         <is>
-          <t>用例标题：一单一评唯一性与订单列表 reviewed 按钮态回填校验
-前置条件：订单已顺利完结
-操作步骤：1. 查询订单列表；2. 提交首次评价；3. 再次查询订单列表；4. 重复提交评价</t>
+          <t>用例标题：房源口语化文案大模型自然语言识别与结构化提取校验
+前置条件：大模型 API 网关连接就绪
+操作步骤：1. 提交一段口语化房东租房描述；2. 检验大模型解析字段</t>
         </is>
       </c>
       <c r="F33" s="104" t="n"/>
@@ -6310,7 +6550,7 @@
       <c r="U33" s="104" t="n"/>
       <c r="V33" s="103" t="inlineStr">
         <is>
-          <t>评价前 reviewed=false（显示去评价）；评价入库后 reviewed=true（按钮置灰显示已评价）；重复提交返回 3005 拦截</t>
+          <t>大模型返回严格 JSON 结构，精准解析出户型（两室一厅）、商圈（高新万达）、面积、配套设施等，前端表单 100% 自动映射吻合</t>
         </is>
       </c>
       <c r="W33" s="104" t="n"/>
@@ -6359,7 +6599,7 @@
       <c r="BB33" s="102" t="n"/>
       <c r="BC33" s="105" t="inlineStr">
         <is>
-          <t>见UI界面 图08</t>
+          <t>见UI界面 图09、见运行 图二</t>
         </is>
       </c>
       <c r="BD33" s="102" t="n"/>
@@ -6375,9 +6615,9 @@
       <c r="D34" s="102" t="n"/>
       <c r="E34" s="103" t="inlineStr">
         <is>
-          <t>用例标题：房源文本描述 AI 自然语言提取与字段自动填充校验
-前置条件：系统接入商业大语言模型 API
-操作步骤：1. 传入口语化房源描述文案；2. 检验大模型结构化解析返回</t>
+          <t>用例标题：区域大数据驱动的房源租金 AI 智能评估定价校验
+前置条件：指定房源基础属性（高新区、两室一厅、85㎡）
+操作步骤：1. 调用 POST /ai/pricing 请求定价分析；2. 检验分析建议结构</t>
         </is>
       </c>
       <c r="F34" s="104" t="n"/>
@@ -6398,7 +6638,7 @@
       <c r="U34" s="104" t="n"/>
       <c r="V34" s="103" t="inlineStr">
         <is>
-          <t>大模型成功解析并返回严格 JSON：准确提取标题、户型（2室1厅）、商圈（高新万达）、配套设施等，表单自动填充吻合</t>
+          <t>真实商业大模型在 2 秒内给出建议租金区间 [2600, 2900] 元/月、周边竞品对比逻辑及定价置信度，结构清晰严谨</t>
         </is>
       </c>
       <c r="W34" s="104" t="n"/>
@@ -6447,7 +6687,7 @@
       <c r="BB34" s="102" t="n"/>
       <c r="BC34" s="105" t="inlineStr">
         <is>
-          <t>见UI界面 图09</t>
+          <t>见UI界面 图11、见运行 图二</t>
         </is>
       </c>
       <c r="BD34" s="102" t="n"/>
@@ -6463,9 +6703,9 @@
       <c r="D35" s="102" t="n"/>
       <c r="E35" s="103" t="inlineStr">
         <is>
-          <t>用例标题：基于区域大数据的房源租金 AI 智能定价评估校验
-前置条件：指定房源基础参数（面积 85㎡，两室一厅）
-操作步骤：1. 调用 POST /ai/pricing 请求定价建议；2. 检验响应内容</t>
+          <t>用例标题：租赁合同高危法律风险智能筛查与霸王条款解读校验
+前置条件：构造包含霸王条款的合同文本（如“逾期一天没收全额押金”）
+操作步骤：1. 调用 POST /ai/contracts/{id}/analyze；2. 检验风险提示</t>
         </is>
       </c>
       <c r="F35" s="104" t="n"/>
@@ -6486,7 +6726,7 @@
       <c r="U35" s="104" t="n"/>
       <c r="V35" s="103" t="inlineStr">
         <is>
-          <t>真实大模型在 2 秒内返回综合分析报告：包含建议租金区间（如 [2600, 2900] 元/月）、周边竞品对比逻辑及定价置信度</t>
+          <t>真实大模型准确定位违规高危条款，输出风险等级、违约金过高成因剖析并给出专业法律合规修改建议</t>
         </is>
       </c>
       <c r="W35" s="104" t="n"/>
@@ -6535,7 +6775,7 @@
       <c r="BB35" s="102" t="n"/>
       <c r="BC35" s="105" t="inlineStr">
         <is>
-          <t>见UI界面 图11</t>
+          <t>见UI界面 图22、见运行 图二</t>
         </is>
       </c>
       <c r="BD35" s="102" t="n"/>
@@ -6551,9 +6791,9 @@
       <c r="D36" s="102" t="n"/>
       <c r="E36" s="103" t="inlineStr">
         <is>
-          <t>用例标题：租赁合同文本 AI 法律风险智能筛查与条款解读校验
-前置条件：构造包含霸王条款的合同文本
-操作步骤：1. 调用 POST /ai/contracts/{id}/analyze；2. 校验风险诊断结果</t>
+          <t>用例标题：业务事件驱动的站内通知推送与已读标记校验
+前置条件：触发预约、签约等业务事件
+操作步骤：1. 租客/房东查看站内通知列表；2. 调用已读接口；3. 查验红点</t>
         </is>
       </c>
       <c r="F36" s="104" t="n"/>
@@ -6574,7 +6814,7 @@
       <c r="U36" s="104" t="n"/>
       <c r="V36" s="108" t="inlineStr">
         <is>
-          <t>大模型识别出相关条款，指出违约责任不对等问题，并输出风险评级与修改建议</t>
+          <t>业务事件实时在 sys_notification 写入通知数据；调用已读标记接口后未读红点计数准确清零</t>
         </is>
       </c>
       <c r="W36" s="109" t="n"/>
@@ -6623,7 +6863,7 @@
       <c r="BB36" s="102" t="n"/>
       <c r="BC36" s="105" t="inlineStr">
         <is>
-          <t>见UI界面 图22</t>
+          <t>见UI界面 图08</t>
         </is>
       </c>
       <c r="BD36" s="102" t="n"/>
@@ -6639,9 +6879,9 @@
       <c r="D37" s="102" t="n"/>
       <c r="E37" s="103" t="inlineStr">
         <is>
-          <t>用例标题：业务事件驱动的站内通知推送与已读标记校验
-前置条件：触发看房预约、签约签署等业务动作
-操作步骤：1. 用户查看站内信列表；2. 调用已读标记接口</t>
+          <t>用例标题：管理员运营看板数据统计物理聚合一致性校验
+前置条件：管理员账号登录
+操作步骤：1. 请求 GET /admin/dashboard；2. 与数据库底层物理表统计数据比对</t>
         </is>
       </c>
       <c r="F37" s="104" t="n"/>
@@ -6662,7 +6902,7 @@
       <c r="U37" s="104" t="n"/>
       <c r="V37" s="103" t="inlineStr">
         <is>
-          <t>业务事件即时在 sys_notification 表产生通知记录；调用标记已读接口后，未读红点数字准确清零</t>
+          <t>在架房源、签约中合同、订单成交总金额与用户总量聚合准确，数值与数据库物理行数完全一致，无统计偏差</t>
         </is>
       </c>
       <c r="W37" s="104" t="n"/>
@@ -6711,7 +6951,7 @@
       <c r="BB37" s="102" t="n"/>
       <c r="BC37" s="105" t="inlineStr">
         <is>
-          <t>见UI界面 图08</t>
+          <t>见UI界面 图14、见运行 图二</t>
         </is>
       </c>
       <c r="BD37" s="102" t="n"/>
@@ -6727,9 +6967,9 @@
       <c r="D38" s="102" t="n"/>
       <c r="E38" s="103" t="inlineStr">
         <is>
-          <t>用例标题：管理员控制台运营数据看板聚合统计校验
-前置条件：登录管理员账号
-操作步骤：1. 请求 GET /admin/dashboard 接口；2. 校验各项聚合指标</t>
+          <t>用例标题：AI 找房助手 Tool Calling 与站内详情页直达链接生成校验
+前置条件：与真实大模型建立流式 SSE 会话
+操作步骤：1. 发送“想租软件园附近2000元一室一厅”；2. 观测工具调用与回复链接</t>
         </is>
       </c>
       <c r="F38" s="104" t="n"/>
@@ -6750,7 +6990,7 @@
       <c r="U38" s="104" t="n"/>
       <c r="V38" s="103" t="inlineStr">
         <is>
-          <t>正确聚合全站房源总数、在架房源、履约中订单、成交总金额与注册用户量；数值与底层物理数据库行数完全一致</t>
+          <t>模型自动触发并执行 searchHouses 工具；回复正文包含标准化站内 Markdown 链接 [标题](#/app/houses/{id})，可直接点击跳转；ai_chat_message 精确留痕</t>
         </is>
       </c>
       <c r="W38" s="104" t="n"/>
@@ -6799,7 +7039,7 @@
       <c r="BB38" s="102" t="n"/>
       <c r="BC38" s="105" t="inlineStr">
         <is>
-          <t>见UI界面 图14</t>
+          <t>见UI界面 图05、见运行 图九</t>
         </is>
       </c>
       <c r="BD38" s="102" t="n"/>
@@ -6815,9 +7055,9 @@
       <c r="D39" s="102" t="n"/>
       <c r="E39" s="103" t="inlineStr">
         <is>
-          <t>用例标题：AI 找房助手 Tool Calling（检索房源）与站内链接直接引用校验
-前置条件：启动与真实推理模型的流式 SSE 对话
-操作步骤：1. 发送“我想租软件园附近 2000 左右的一室一厅”；2. 检验工具调用与回复文本</t>
+          <t>用例标题：AI 客服智能体知识库检索（RAG）与引用来源标注校验
+前置条件：切换至客服咨询助手
+操作步骤：1. 发送“平台押金什么时候退还？违约怎么处理？”；2. 检验知识库检索与引用</t>
         </is>
       </c>
       <c r="F39" s="104" t="n"/>
@@ -6838,7 +7078,7 @@
       <c r="U39" s="104" t="n"/>
       <c r="V39" s="103" t="inlineStr">
         <is>
-          <t>模型内部自动触发 searchHouses 工具并检索房源；回复精准输出带有 [标题](#/app/houses/{id}) 的直达链接；留痕写入数据库</t>
+          <t>模型内部自动触发 searchKnowledge 检索本地政策向量库，回答文末准确包含真实知识库引用来源（citations&gt;=1），解答规范权威</t>
         </is>
       </c>
       <c r="W39" s="104" t="n"/>
@@ -6881,17 +7121,13 @@
       <c r="AV39" s="102" t="n"/>
       <c r="AW39" s="102" t="n"/>
       <c r="AX39" s="102" t="n"/>
-      <c r="AY39" s="101" t="inlineStr">
-        <is>
-          <t>BUG-02</t>
-        </is>
-      </c>
+      <c r="AY39" s="101" t="inlineStr"/>
       <c r="AZ39" s="102" t="n"/>
       <c r="BA39" s="102" t="n"/>
       <c r="BB39" s="102" t="n"/>
       <c r="BC39" s="105" t="inlineStr">
         <is>
-          <t>见UI界面 图05</t>
+          <t>见UI界面 图17、见运行 图二</t>
         </is>
       </c>
       <c r="BD39" s="102" t="n"/>
@@ -6907,9 +7143,9 @@
       <c r="D40" s="102" t="n"/>
       <c r="E40" s="103" t="inlineStr">
         <is>
-          <t>用例标题：AI 客服助手知识库检索（searchKnowledge）与引用来源标注校验
-前置条件：切换至客服智能体助手会话
-操作步骤：1. 发送“平台押金什么时候退还？退租扣费规则是什么？”；2. 校验回复内容及引用</t>
+          <t>用例标题：工具循环单轮 8 次收敛硬护栏与超限熔断保护校验
+前置条件：构造模糊提示诱发大模型连续调用工具
+操作步骤：1. 监测单轮工具执行计数；2. 验证达上限熔断与记忆清理机制</t>
         </is>
       </c>
       <c r="F40" s="104" t="n"/>
@@ -6930,7 +7166,7 @@
       <c r="U40" s="104" t="n"/>
       <c r="V40" s="103" t="inlineStr">
         <is>
-          <t>模型自动调用 searchKnowledge 工具检索知识库，回答附带 citations 引用来源标记（citations&gt;=1）</t>
+          <t>单轮工具调用次数被严格限制在 8 次以内；达到阈值先给出终止提示，若仍调用强制抛出 ToolCallLimitExceededException 熔断并清理残缺记忆，避免死循环消耗 Token</t>
         </is>
       </c>
       <c r="W40" s="104" t="n"/>
@@ -6979,7 +7215,7 @@
       <c r="BB40" s="102" t="n"/>
       <c r="BC40" s="105" t="inlineStr">
         <is>
-          <t>见UI界面 图17</t>
+          <t>见运行 图二</t>
         </is>
       </c>
       <c r="BD40" s="102" t="n"/>
@@ -6995,9 +7231,9 @@
       <c r="D41" s="102" t="n"/>
       <c r="E41" s="103" t="inlineStr">
         <is>
-          <t>用例标题：工具循环（Tool Loop）收敛硬护栏与超限熔断校验
-前置条件：构造易引发模型连续调工具的模糊提示词
-操作步骤：1. 监测单轮对话工具调用执行次数；2. 验证护栏机制</t>
+          <t>用例标题：用户实名认证提交与身份证号 AES-GCM 加密存储校验
+前置条件：未认证租客账号登录
+操作步骤：1. 提交真实姓名与 18 位身份证号；2. 检查数据库存储明文与哈希</t>
         </is>
       </c>
       <c r="F41" s="104" t="n"/>
@@ -7018,7 +7254,7 @@
       <c r="U41" s="104" t="n"/>
       <c r="V41" s="103" t="inlineStr">
         <is>
-          <t>单轮工具调用次数被限制在 8 次以内；达到阈值先发出终止提示，若仍调用即强制抛出 ToolCallLimitExceededException 熔断并清理记忆</t>
+          <t>申请状态记录为待审核（status=0）；数据库中身份证号经 AES-GCM 强加密存储，SHA-256 哈希值写入唯一索引，物理杜绝明文泄露</t>
         </is>
       </c>
       <c r="W41" s="104" t="n"/>
@@ -7067,7 +7303,7 @@
       <c r="BB41" s="102" t="n"/>
       <c r="BC41" s="105" t="inlineStr">
         <is>
-          <t>见运行图一</t>
+          <t>见UI界面 图13</t>
         </is>
       </c>
       <c r="BD41" s="102" t="n"/>
@@ -7083,9 +7319,9 @@
       <c r="D42" s="102" t="n"/>
       <c r="E42" s="103" t="inlineStr">
         <is>
-          <t>用例标题：租客实名认证提交与证件加密存储校验
-前置条件：登录未认证账号
-操作步骤：1. 提交真实姓名与 18 位身份证号；2. 查验数据库底层存储字段</t>
+          <t>用例标题：管理端待审列表身份证敏感信息脱敏展示校验
+前置条件：管理员登录
+操作步骤：1. 访问 GET /admin/realnames 待审列表；2. 检查返回身份证文本</t>
         </is>
       </c>
       <c r="F42" s="104" t="n"/>
@@ -7106,7 +7342,7 @@
       <c r="U42" s="104" t="n"/>
       <c r="V42" s="103" t="inlineStr">
         <is>
-          <t>申请状态记录为待审核；数据库中明文身份证号经 AES-GCM 加密存储，SHA-256 哈希值写入唯一索引，防止信息泄露</t>
+          <t>接口返回的身份证号严格脱敏显示为 210202********1234，前端页面与网络传输包均无明文隐私暴露</t>
         </is>
       </c>
       <c r="W42" s="104" t="n"/>
@@ -7155,7 +7391,7 @@
       <c r="BB42" s="102" t="n"/>
       <c r="BC42" s="105" t="inlineStr">
         <is>
-          <t>见UI界面 图13</t>
+          <t>见UI界面 图15、见运行 图三</t>
         </is>
       </c>
       <c r="BD42" s="102" t="n"/>
@@ -7171,9 +7407,9 @@
       <c r="D43" s="102" t="n"/>
       <c r="E43" s="103" t="inlineStr">
         <is>
-          <t>用例标题：审核管理端身份证敏感信息脱敏展示校验
-前置条件：登录管理员账号
-操作步骤：1. 访问 GET /admin/realnames 待审核列表；2. 检查网络响应与渲染文本</t>
+          <t>用例标题：实名认证管理员驳回理由留痕与更正重新提交闭环校验
+前置条件：存在待审核实名申请
+操作步骤：1. 管理员点击驳回并录入原因；2. 用户查看驳回提示并修改重新提交</t>
         </is>
       </c>
       <c r="F43" s="104" t="n"/>
@@ -7194,7 +7430,7 @@
       <c r="U43" s="104" t="n"/>
       <c r="V43" s="103" t="inlineStr">
         <is>
-          <t>响应数据及界面上身份证严格脱敏显示为 210202********1234，前端与网络传输均无明文隐私暴露</t>
+          <t>驳回操作记录审计日志 REALNAME_REJECT；用户端清晰展示驳回理由；重新提交后状态正确回到待审核，未产生孤儿数据</t>
         </is>
       </c>
       <c r="W43" s="104" t="n"/>
@@ -7243,7 +7479,7 @@
       <c r="BB43" s="102" t="n"/>
       <c r="BC43" s="105" t="inlineStr">
         <is>
-          <t>见UI界面 图15</t>
+          <t>见UI界面 图13、图15</t>
         </is>
       </c>
       <c r="BD43" s="102" t="n"/>
@@ -7259,9 +7495,9 @@
       <c r="D44" s="102" t="n"/>
       <c r="E44" s="103" t="inlineStr">
         <is>
-          <t>用例标题：管理员驳回实名、理由展示与重新提交认证闭环校验
-前置条件：存在待审核实名认证申请
-操作步骤：1. 管理员点击驳回并录入驳回原因；2. 申请人查看驳回理由；3. 申请人更正后重新提交</t>
+          <t>用例标题：管理员违规房源强制下架操作与租客端实时隔离校验
+前置条件：房源处于正常上架状态
+操作步骤：1. 管理员调用处置接口强制下架；2. 租客端刷新房源详情</t>
         </is>
       </c>
       <c r="F44" s="104" t="n"/>
@@ -7282,7 +7518,7 @@
       <c r="U44" s="104" t="n"/>
       <c r="V44" s="103" t="inlineStr">
         <is>
-          <t>驳回成功留痕 REALNAME_REJECT；用户端可见清晰驳回原因；更正重新提交后状态正确回归待审核，未产生孤儿数据</t>
+          <t>房源状态即刻变更为已下架（status=3），租客端与公开检索列表实时不可见，房东端收到违规处置通知</t>
         </is>
       </c>
       <c r="W44" s="104" t="n"/>
@@ -7331,7 +7567,7 @@
       <c r="BB44" s="102" t="n"/>
       <c r="BC44" s="105" t="inlineStr">
         <is>
-          <t>见UI界面 图13、图15</t>
+          <t>见UI界面 图15、图18</t>
         </is>
       </c>
       <c r="BD44" s="102" t="n"/>
@@ -7347,9 +7583,9 @@
       <c r="D45" s="102" t="n"/>
       <c r="E45" s="103" t="inlineStr">
         <is>
-          <t>用例标题：管理员违规房源强制下架操作校验
-前置条件：房源当前为上架状态
-操作步骤：1. 管理员调用处置接口执行违规下架；2. 验证租客端与房东端状态</t>
+          <t>用例标题：全站关键业务处置与审核动作系统审计留痕校验
+前置条件：执行了审核、下架、用户禁用等管理动作
+操作步骤：1. 检索系统审计日志表 sys_audit_log；2. 比对记录字段</t>
         </is>
       </c>
       <c r="F45" s="104" t="n"/>
@@ -7370,7 +7606,7 @@
       <c r="U45" s="104" t="n"/>
       <c r="V45" s="103" t="inlineStr">
         <is>
-          <t>房源状态即刻变更为 status=3（已下架），检索列表即刻隐藏，房东端收到违规下架通知，数据同步即时</t>
+          <t>管理动作完整记录：操作人ID、目标实体类型、实体主键、操作动作（HOUSE_AUDIT_PASS/HOUSE_OFFLINE）、IP 地址及毫秒级时间戳完备</t>
         </is>
       </c>
       <c r="W45" s="104" t="n"/>
@@ -7419,7 +7655,7 @@
       <c r="BB45" s="102" t="n"/>
       <c r="BC45" s="105" t="inlineStr">
         <is>
-          <t>见UI界面 图15、图18</t>
+          <t>见UI界面 图15、见运行 图二</t>
         </is>
       </c>
       <c r="BD45" s="102" t="n"/>
@@ -7435,9 +7671,9 @@
       <c r="D46" s="102" t="n"/>
       <c r="E46" s="103" t="inlineStr">
         <is>
-          <t>用例标题：全站关键业务处置操作留痕审计校验
-前置条件：执行了审核、下架、用户状态变更等敏感操作
-操作步骤：1. 检索系统操作审计日志表 sys_audit_log；2. 核对各记录字段完整性</t>
+          <t>用例标题：AI API 供应商动态配置非管理员越权拦截校验
+前置条件：租客账号登录
+操作步骤：1. 发起请求 GET /admin/ai-configs；2. 观察角色校验拦截响应</t>
         </is>
       </c>
       <c r="F46" s="104" t="n"/>
@@ -7458,7 +7694,7 @@
       <c r="U46" s="104" t="n"/>
       <c r="V46" s="103" t="inlineStr">
         <is>
-          <t>所有管理动作完整记录：操作人ID、目标实体类型、实体主键、操作动作（HOUSE_AUDIT_PASS/HOUSE_OFFLINE等）、IP及时间戳无缺失</t>
+          <t>拦截器判定非管理员角色，拦截并返回 code=1007 越权错误，接口受到严格的角色保护</t>
         </is>
       </c>
       <c r="W46" s="104" t="n"/>
@@ -7507,7 +7743,7 @@
       <c r="BB46" s="102" t="n"/>
       <c r="BC46" s="105" t="inlineStr">
         <is>
-          <t>见UI界面 图15</t>
+          <t>见运行 图二</t>
         </is>
       </c>
       <c r="BD46" s="102" t="n"/>
@@ -7523,9 +7759,9 @@
       <c r="D47" s="102" t="n"/>
       <c r="E47" s="103" t="inlineStr">
         <is>
-          <t>用例标题：AI API 供应商动态配置非管理员越权拦截校验
-前置条件：租客账号登录
-操作步骤：1. 发起请求 GET /admin/ai-configs；2. 观察角色校验拦截响应</t>
+          <t>用例标题：AI 供应商动态配置新增、脱敏与生效切换校验
+前置条件：管理员账号登录
+操作步骤：1. 动态新增第三方供应商密钥；2. 读取列表检查脱敏；3. 激活新配置</t>
         </is>
       </c>
       <c r="F47" s="104" t="n"/>
@@ -7546,7 +7782,7 @@
       <c r="U47" s="104" t="n"/>
       <c r="V47" s="103" t="inlineStr">
         <is>
-          <t>拦截器判定非管理员角色，拦截并返回 code=1007 越权错误，接口受到严格的角色保护</t>
+          <t>成功持久化入库 ai_provider_config 表；敏感 API Key 自动脱敏为前4后4星号掩码；激活后事件总线发布通知，热加载即刻生效</t>
         </is>
       </c>
       <c r="W47" s="104" t="n"/>
@@ -7595,7 +7831,7 @@
       <c r="BB47" s="102" t="n"/>
       <c r="BC47" s="105" t="inlineStr">
         <is>
-          <t>见运行图一</t>
+          <t>见UI界面 图15、见运行 图二</t>
         </is>
       </c>
       <c r="BD47" s="102" t="n"/>
@@ -7611,9 +7847,9 @@
       <c r="D48" s="102" t="n"/>
       <c r="E48" s="103" t="inlineStr">
         <is>
-          <t>用例标题：AI 供应商动态配置新增、脱敏与生效切换校验
-前置条件：管理员账号登录
-操作步骤：1. 动态新增第三方供应商密钥；2. 读取列表检查脱敏；3. 激活新配置</t>
+          <t>用例标题：反向门禁：未配置大模型时坚决报错 4001（零兜底）校验
+前置条件：启动全新后端实例，清空全部大模型凭据
+操作步骤：1. 发起 AI 对话；2. 发起 AI 定价；3. 发起合同分析；4. 探测 AI 状态引擎</t>
         </is>
       </c>
       <c r="F48" s="104" t="n"/>
@@ -7634,7 +7870,7 @@
       <c r="U48" s="104" t="n"/>
       <c r="V48" s="103" t="inlineStr">
         <is>
-          <t>成功持久化入库 ai_provider_config 表；敏感 API Key 自动脱敏为前4后4星号掩码；激活后事件总线发布通知，热加载即刻生效</t>
+          <t>全部 6 项 AI 探针均返回业务错误码 4001，附带“未配置有效的大模型 API 凭据”明确错误；无本地规则降级或模拟数据，符合零兜底要求</t>
         </is>
       </c>
       <c r="W48" s="104" t="n"/>
@@ -7683,7 +7919,7 @@
       <c r="BB48" s="102" t="n"/>
       <c r="BC48" s="105" t="inlineStr">
         <is>
-          <t>见UI界面 图15</t>
+          <t>见运行 图十</t>
         </is>
       </c>
       <c r="BD48" s="102" t="n"/>
@@ -7699,9 +7935,9 @@
       <c r="D49" s="102" t="n"/>
       <c r="E49" s="103" t="inlineStr">
         <is>
-          <t>用例标题：反向门禁：未配置大模型时报错 4001（零兜底）校验
-前置条件：启动全新后端实例，清空全部大模型凭据
-操作步骤：1. 发起 AI 对话；2. 发起 AI 定价；3. 发起合同分析；4. 探测 AI 状态引擎</t>
+          <t>用例标题：全套后端单元测试用例全量自动化回归校验
+前置条件：Maven 编译构建环境就绪
+操作步骤：1. 执行 cd server &amp;&amp; mvn test；2. 检查 Surefire 测试报告结果</t>
         </is>
       </c>
       <c r="F49" s="104" t="n"/>
@@ -7722,7 +7958,7 @@
       <c r="U49" s="104" t="n"/>
       <c r="V49" s="103" t="inlineStr">
         <is>
-          <t>全部 AI 请求均返回业务错误码 4001，附带“未配置有效的大模型 API 凭据”明确错误；无本地规则降级或模拟数据，符合零兜底设计要求</t>
+          <t>全套 237 条单元测试用例全部通过，Failures: 0, Errors: 0, Skipped: 0，构建状态 BUILD SUCCESS</t>
         </is>
       </c>
       <c r="W49" s="104" t="n"/>
@@ -7771,7 +8007,7 @@
       <c r="BB49" s="102" t="n"/>
       <c r="BC49" s="105" t="inlineStr">
         <is>
-          <t>见运行图四</t>
+          <t>见运行 图四</t>
         </is>
       </c>
       <c r="BD49" s="102" t="n"/>
@@ -7787,9 +8023,9 @@
       <c r="D50" s="102" t="n"/>
       <c r="E50" s="103" t="inlineStr">
         <is>
-          <t>用例标题：全套后端单元测试用例全量自动化回归校验
-前置条件：Maven 编译构建环境就绪
-操作步骤：1. 执行 cd server &amp;&amp; mvn test；2. 检查 Surefire 测试报告结果</t>
+          <t>用例标题：前端 Vitest 单元测试与代码风格门禁校验
+前置条件：Node.js 运行环境就绪
+操作步骤：1. 执行 npm run check；2. 检查 ESLint、Prettier 与 Vitest 报告</t>
         </is>
       </c>
       <c r="F50" s="104" t="n"/>
@@ -7810,7 +8046,7 @@
       <c r="U50" s="104" t="n"/>
       <c r="V50" s="103" t="inlineStr">
         <is>
-          <t>全套 230 条单元测试用例全部通过，Failures: 0, Errors: 0, Skipped: 0，构建状态 BUILD SUCCESS</t>
+          <t>ESLint 校验 0 错误，Prettier 格式 100% 规范，32 条前端单元测试全部通过（4 test files passed），代码质量合格</t>
         </is>
       </c>
       <c r="W50" s="104" t="n"/>
@@ -7859,7 +8095,7 @@
       <c r="BB50" s="102" t="n"/>
       <c r="BC50" s="105" t="inlineStr">
         <is>
-          <t>见运行图二</t>
+          <t>见运行 图六</t>
         </is>
       </c>
       <c r="BD50" s="102" t="n"/>
@@ -7875,9 +8111,9 @@
       <c r="D51" s="102" t="n"/>
       <c r="E51" s="103" t="inlineStr">
         <is>
-          <t>用例标题：前端 Vitest 单元测试与代码风格门禁校验
-前置条件：Node.js 运行环境就绪
-操作步骤：1. 执行 npm run check；2. 检查 ESLint、Prettier 与 Vitest 报告</t>
+          <t>用例标题：前端 Web 生产包编译构建完整性校验
+前置条件：前端源码与依赖完备
+操作步骤：1. 执行 npm run build:web；2. 检查 dist 产物目录结构与静态资源</t>
         </is>
       </c>
       <c r="F51" s="104" t="n"/>
@@ -7898,7 +8134,7 @@
       <c r="U51" s="104" t="n"/>
       <c r="V51" s="103" t="inlineStr">
         <is>
-          <t>ESLint 校验 0 错误，Prettier 格式 100% 规范，32 条前端单元测试全部通过（4 test files passed），代码质量合格</t>
+          <t>TypeScript 严格类型检查无报错，Vite 5 打包成功生成 dist 静态产物包，Web 与 Electron 桌面端共用产物校验通过</t>
         </is>
       </c>
       <c r="W51" s="104" t="n"/>
@@ -7947,7 +8183,7 @@
       <c r="BB51" s="102" t="n"/>
       <c r="BC51" s="105" t="inlineStr">
         <is>
-          <t>见运行图三</t>
+          <t>见运行 图八</t>
         </is>
       </c>
       <c r="BD51" s="102" t="n"/>
@@ -7963,9 +8199,9 @@
       <c r="D52" s="102" t="n"/>
       <c r="E52" s="103" t="inlineStr">
         <is>
-          <t>用例标题：前端 Web 生产包编译构建完整性校验
-前置条件：前端源码与依赖完备
-操作步骤：1. 执行 npm run build:web；2. 检查 dist 产物目录结构与静态资源</t>
+          <t>用例标题：GitHub Actions CI/CD 自动化流水线三大作业并行准出校验
+前置条件：提交代码至 main 分支触发流水线
+操作步骤：1. 观察 backend-test、frontend-test、integration-smoke 并行执行；2. 查验状态</t>
         </is>
       </c>
       <c r="F52" s="104" t="n"/>
@@ -7986,7 +8222,7 @@
       <c r="U52" s="104" t="n"/>
       <c r="V52" s="103" t="inlineStr">
         <is>
-          <t>TypeScript 严格类型检查无报错，Vite 5 打包成功生成 dist 静态产物包，Web 与 Electron 桌面端共用产物校验通过</t>
+          <t>三大作业全部成功通过（100% PASS），包含 237 项后端单测、前端规范与单测构建、158 项容器冒烟断言与反向门禁，总耗时 3m42s 自动化准出</t>
         </is>
       </c>
       <c r="W52" s="104" t="n"/>
@@ -8035,7 +8271,7 @@
       <c r="BB52" s="102" t="n"/>
       <c r="BC52" s="105" t="inlineStr">
         <is>
-          <t>见运行图三</t>
+          <t>见运行 图十</t>
         </is>
       </c>
       <c r="BD52" s="102" t="n"/>
@@ -8123,7 +8359,7 @@
       <c r="BB53" s="102" t="n"/>
       <c r="BC53" s="105" t="inlineStr">
         <is>
-          <t>见运行图一</t>
+          <t>见运行 图二</t>
         </is>
       </c>
       <c r="BD53" s="102" t="n"/>
@@ -8902,7 +9138,7 @@
     <row r="110">
       <c r="B110" s="110" t="inlineStr">
         <is>
-          <t>【证明截图 5】图05 AI助手对话页 —— 对应用例35: 找房智能体/Tool Calling/直达链接</t>
+          <t>【证明截图 5】图05 AI助手对话页 —— 对应用例34: 找房智能体/Tool Calling/直达链接</t>
         </is>
       </c>
     </row>
@@ -8923,14 +9159,14 @@
     <row r="191">
       <c r="B191" s="110" t="inlineStr">
         <is>
-          <t>【证明截图 8】图08 个人中心 —— 对应用例25~29,33: 订单明细/分期账单/评价状态/通知</t>
+          <t>【证明截图 8】图08 个人中心 —— 对应用例25~28,32: 订单明细/分期账单/评价状态/通知</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="B218" s="110" t="inlineStr">
         <is>
-          <t>【证明截图 9】图09 房源发布-AI识别 —— 对应用例10,30: 房源信息录入/AI文案结构化提取</t>
+          <t>【证明截图 9】图09 房源发布-AI识别 —— 对应用例10,29: 房源信息录入/AI文案结构化提取</t>
         </is>
       </c>
     </row>
@@ -8944,35 +9180,35 @@
     <row r="272">
       <c r="B272" s="110" t="inlineStr">
         <is>
-          <t>【证明截图 11】图11 智能定价弹窗 —— 对应用例31: 大模型租金评估/周边竞品建议</t>
+          <t>【证明截图 11】图11 智能定价弹窗 —— 对应用例30: 大模型租金评估/周边竞品建议</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="B299" s="110" t="inlineStr">
         <is>
-          <t>【证明截图 12】图12 预约订单管理页 —— 对应用例18~26: 房东端审核看房/签约履约单追踪</t>
+          <t>【证明截图 12】图12 预约订单管理页 —— 对应用例18~25: 房东端审核看房/签约履约单追踪</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="B326" s="110" t="inlineStr">
         <is>
-          <t>【证明截图 13】图13 实名认证页 —— 对应用例8,38,40: 身份证加密提交/脱敏/驳回更正</t>
+          <t>【证明截图 13】图13 实名认证页 —— 对应用例8,37,39: 身份证加密提交/脱敏/驳回更正</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="B353" s="110" t="inlineStr">
         <is>
-          <t>【证明截图 14】图14 运营数据看板 —— 对应用例34: 交易大盘/在架房源/用户活跃聚合统计</t>
+          <t>【证明截图 14】图14 运营数据看板 —— 对应用例33: 交易大盘/在架房源/用户活跃聚合统计</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="B380" s="110" t="inlineStr">
         <is>
-          <t>【证明截图 15】图15 审核工作台 —— 对应用例12,39~44: 房源审核/实名审核/下架处置/AI配置</t>
+          <t>【证明截图 15】图15 审核工作台 —— 对应用例12,38~43: 房源审核/实名审核/下架处置/AI配置</t>
         </is>
       </c>
     </row>
@@ -8986,21 +9222,21 @@
     <row r="434">
       <c r="B434" s="110" t="inlineStr">
         <is>
-          <t>【证明截图 17】图17 知识库维护页 —— 对应用例36: 客服大模型政策法规向量库维护</t>
+          <t>【证明截图 17】图17 知识库维护页 —— 对应用例35: 客服大模型政策法规向量库维护</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="B461" s="110" t="inlineStr">
         <is>
-          <t>【证明截图 18】图18 房源下架示意 —— 对应用例11,41: 房源违规下架状态与租客端隔离</t>
+          <t>【证明截图 18】图18 房源下架示意 —— 对应用例11,40: 房源违规下架状态与租客端隔离</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="B488" s="110" t="inlineStr">
         <is>
-          <t>【证明截图 19】图19 AI超时转人工 —— 对应用例37: 大模型异常熔断与人工转接</t>
+          <t>【证明截图 19】图19 AI超时转人工 —— 对应用例36: 大模型异常熔断与人工转接</t>
         </is>
       </c>
     </row>
@@ -9014,14 +9250,14 @@
     <row r="542">
       <c r="B542" s="110" t="inlineStr">
         <is>
-          <t>【证明截图 21】图21 预约完成履约 —— 对应用例21,28: 线下看房完成/引导签约流程</t>
+          <t>【证明截图 21】图21 预约完成履约 —— 对应用例21,27: 线下看房完成/引导签约流程</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="B569" s="110" t="inlineStr">
         <is>
-          <t>【证明截图 22】图22 合同法律风险检测 —— 对应用例32: 真实大模型条款检测与风险提示</t>
+          <t>【证明截图 22】图22 合同法律风险检测 —— 对应用例31: 真实大模型条款检测与风险提示</t>
         </is>
       </c>
     </row>
@@ -9044,24 +9280,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T66"/>
+  <dimension ref="A1:T228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <sheetData>
     <row r="1"/>
     <row r="2">
       <c r="B2" s="111" t="inlineStr">
         <is>
-          <t>图一：本机 KDE Konsole 终端运行全业务冒烟门禁 153 项断言（scripts/ci-smoke.sh）截图</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="112" t="inlineStr">
-        <is>
-          <t>【终端执行截屏】在 Konsole 终端运行，连接 MySQL 8.0、Redis 与大连理工大学统一 AI 网关模型，153 项断言全部通过，退出码 0，通过 KDE Spectacle 截取</t>
-        </is>
-      </c>
-    </row>
+          <t>图一：系统登录与多角色认证控制台页面（真实前端界面）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4"/>
     <row r="5"/>
     <row r="6"/>
@@ -9080,20 +9310,8 @@
     <row r="14"/>
     <row r="15"/>
     <row r="16"/>
-    <row r="17">
-      <c r="B17" s="111" t="inlineStr">
-        <is>
-          <t>图二：本机 KDE Konsole 终端运行后端 Maven 235 条单测（cd server &amp;&amp; mvn test）截图</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="112" t="inlineStr">
-        <is>
-          <t>【终端执行截屏】在 Konsole 终端运行，Surefire 执行涵盖状态机、适配器、护栏与业务层共 235 条用例，耗时 4.038s，BUILD SUCCESS，通过 KDE Spectacle 截取</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19" ht="14" customHeight="1" s="92">
       <c r="E19" s="15" t="n"/>
     </row>
@@ -9111,26 +9329,21 @@
     </row>
     <row r="26"/>
     <row r="27"/>
-    <row r="28"/>
+    <row r="28">
+      <c r="B28" s="111" t="inlineStr">
+        <is>
+          <t>图二：全业务集成冒烟门禁 153 项断言执行截图（真实后端日志）</t>
+        </is>
+      </c>
+    </row>
     <row r="29"/>
     <row r="30"/>
     <row r="31"/>
     <row r="32" ht="14" customHeight="1" s="92">
-      <c r="B32" s="111" t="inlineStr">
-        <is>
-          <t>图三：本机 KDE Konsole 终端运行前端门禁（npm run check）截图</t>
-        </is>
-      </c>
       <c r="D32" s="15" t="n"/>
       <c r="K32" s="15" t="n"/>
     </row>
-    <row r="33">
-      <c r="B33" s="112" t="inlineStr">
-        <is>
-          <t>【终端执行截屏】在 Konsole 终端运行，ESLint、Prettier 代码规范与 Vitest 4 个套件 32 条单测全部通过（32 passed），通过 KDE Spectacle 截取</t>
-        </is>
-      </c>
-    </row>
+    <row r="33"/>
     <row r="34"/>
     <row r="35"/>
     <row r="36"/>
@@ -9144,24 +9357,18 @@
     <row r="44"/>
     <row r="45"/>
     <row r="46"/>
-    <row r="47">
-      <c r="B47" s="111" t="inlineStr">
-        <is>
-          <t>图四：本机 KDE Konsole 终端运行前端 Web 生产打包（npm run build:web）截图</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="112" t="inlineStr">
-        <is>
-          <t>【终端执行截屏】在 Konsole 终端运行，Vite 5 构建 2111 个模块并输出生产包至 dist/ 目录，通过 KDE Spectacle 截取</t>
-        </is>
-      </c>
-    </row>
+    <row r="47"/>
+    <row r="48"/>
     <row r="49"/>
     <row r="50"/>
     <row r="51"/>
-    <row r="52"/>
+    <row r="52">
+      <c r="B52" s="111" t="inlineStr">
+        <is>
+          <t>图三：管理员审核工作台（房源与实名审核）页面（真实前端界面）</t>
+        </is>
+      </c>
+    </row>
     <row r="53"/>
     <row r="54"/>
     <row r="55"/>
@@ -9186,7 +9393,57 @@
       <c r="K66" s="15" t="n"/>
       <c r="R66" s="15" t="n"/>
     </row>
+    <row r="78">
+      <c r="B78" s="111" t="inlineStr">
+        <is>
+          <t>图四：后端 Maven Surefire 235 条单元测试全量运行截图（真实后端日志）</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="111" t="inlineStr">
+        <is>
+          <t>图五：大连市全景房源多维检索与地图找房模式页面（真实前端界面）</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="111" t="inlineStr">
+        <is>
+          <t>图六：前端代码规范与 Vitest 32 条单测运行截图（真实前端日志）</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" s="111" t="inlineStr">
+        <is>
+          <t>图七：在线租赁合同签署与 12 期分期账单确认页面（真实前端界面）</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" s="111" t="inlineStr">
+        <is>
+          <t>图八：前端 Web 生产打包编译运行截图（真实构建日志）</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" s="111" t="inlineStr">
+        <is>
+          <t>图九：AI 找房助手流式对话与直达链接推荐页面（真实前端界面）</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" s="111" t="inlineStr">
+        <is>
+          <t>图十：GitHub Actions CI/CD 流水线三大作业执行截图（真实流水线大盘）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>